--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/todos.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/todos.xlsx
@@ -1635,7 +1635,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -48480,7 +48480,7 @@
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F744" t="inlineStr">
@@ -49386,7 +49386,7 @@
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F758" t="inlineStr">
@@ -58800,7 +58800,7 @@
       </c>
       <c r="E904" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F904" t="inlineStr">
@@ -60982,7 +60982,7 @@
       </c>
       <c r="E938" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F938" t="inlineStr">
@@ -61421,7 +61421,7 @@
       </c>
       <c r="E945" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F945" t="inlineStr">
@@ -61868,7 +61868,7 @@
       </c>
       <c r="E952" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F952" t="inlineStr">
@@ -62059,7 +62059,7 @@
       </c>
       <c r="E955" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F955" t="inlineStr">
@@ -62758,7 +62758,7 @@
       </c>
       <c r="E966" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F966" t="inlineStr">
@@ -63721,7 +63721,7 @@
       </c>
       <c r="E981" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F981" t="inlineStr">
@@ -64038,7 +64038,7 @@
       </c>
       <c r="E986" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F986" t="inlineStr">
@@ -64103,7 +64103,7 @@
       </c>
       <c r="E987" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F987" t="inlineStr">
@@ -64294,7 +64294,7 @@
       </c>
       <c r="E990" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F990" t="inlineStr">
@@ -64684,7 +64684,7 @@
       </c>
       <c r="E996" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F996" t="inlineStr">
@@ -64940,7 +64940,7 @@
       </c>
       <c r="E1000" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1000" t="inlineStr">
@@ -65005,7 +65005,7 @@
       </c>
       <c r="E1001" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1001" t="inlineStr">
@@ -65391,7 +65391,7 @@
       </c>
       <c r="E1007" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1007" t="inlineStr">
@@ -66163,7 +66163,7 @@
       </c>
       <c r="E1019" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1019" t="inlineStr">
@@ -66289,7 +66289,7 @@
       </c>
       <c r="E1021" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1021" t="inlineStr">
@@ -66354,7 +66354,7 @@
       </c>
       <c r="E1022" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1022" t="inlineStr">
@@ -66419,7 +66419,7 @@
       </c>
       <c r="E1023" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1023" t="inlineStr">
@@ -66480,7 +66480,7 @@
       </c>
       <c r="E1024" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1024" t="inlineStr">
@@ -66915,7 +66915,7 @@
       </c>
       <c r="E1031" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1031" t="inlineStr">
@@ -67305,7 +67305,7 @@
       </c>
       <c r="E1037" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1037" t="inlineStr">
@@ -67561,7 +67561,7 @@
       </c>
       <c r="E1041" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1041" t="inlineStr">
@@ -67691,7 +67691,7 @@
       </c>
       <c r="E1043" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1043" t="inlineStr">
@@ -67886,7 +67886,7 @@
       </c>
       <c r="E1046" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1046" t="inlineStr">
@@ -67951,7 +67951,7 @@
       </c>
       <c r="E1047" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1047" t="inlineStr">
@@ -68333,7 +68333,7 @@
       </c>
       <c r="E1053" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1053" t="inlineStr">
@@ -68398,7 +68398,7 @@
       </c>
       <c r="E1054" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1054" t="inlineStr">
@@ -69495,7 +69495,7 @@
       </c>
       <c r="E1071" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1071" t="inlineStr">
@@ -70206,7 +70206,7 @@
       </c>
       <c r="E1082" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1082" t="inlineStr">
@@ -70462,7 +70462,7 @@
       </c>
       <c r="E1086" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1086" t="inlineStr">
@@ -71177,7 +71177,7 @@
       </c>
       <c r="E1097" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1097" t="inlineStr">
@@ -71242,7 +71242,7 @@
       </c>
       <c r="E1098" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1098" t="inlineStr">
@@ -71563,7 +71563,7 @@
       </c>
       <c r="E1103" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F1103" t="inlineStr">
